--- a/public/catalog_template.xlsx
+++ b/public/catalog_template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="52">
   <si>
     <t>name</t>
   </si>
@@ -30,6 +30,9 @@
     <t>stock</t>
   </si>
   <si>
+    <t>sku</t>
+  </si>
+  <si>
     <t>available</t>
   </si>
   <si>
@@ -42,6 +45,9 @@
     <t>Dozen of fresh red roses</t>
   </si>
   <si>
+    <t>ROS-12</t>
+  </si>
+  <si>
     <t>Yes</t>
   </si>
   <si>
@@ -54,6 +60,9 @@
     <t>Bright sunflowers in a glass vase</t>
   </si>
   <si>
+    <t>SUN-01</t>
+  </si>
+  <si>
     <t>Orchid Pot</t>
   </si>
   <si>
@@ -63,6 +72,9 @@
     <t>Purple phalaenopsis orchid</t>
   </si>
   <si>
+    <t>ORC-05</t>
+  </si>
+  <si>
     <t>No</t>
   </si>
   <si>
@@ -99,6 +111,9 @@
     <t>stock — quantity available, a whole number. Leave blank if you do not track stock.</t>
   </si>
   <si>
+    <t>sku — your internal product code (e.g. ROS-12). Optional; shown only to you.</t>
+  </si>
+  <si>
     <t>available — "Yes" or "No". Leave blank to default to Yes. Items set to No stay in your list but are hidden from customers.</t>
   </si>
   <si>
@@ -139,6 +154,9 @@
   </si>
   <si>
     <t>stock — cantidad disponible, número entero. Dejala vacía si no llevás control de stock.</t>
+  </si>
+  <si>
+    <t>sku — tu código interno de producto (ej: ROS-12). Opcional; solo lo ves vos.</t>
   </si>
   <si>
     <t>available — "Yes" o "No". Dejala vacía para que sea Yes por defecto. Los ítems en No quedan en tu lista pero ocultos para los clientes.</t>
@@ -573,7 +591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F500"/>
+  <dimension ref="A1:G500"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -581,10 +599,11 @@
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -603,16 +622,19 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2">
         <v>90000</v>
@@ -621,18 +643,21 @@
         <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D3">
         <v>75000</v>
@@ -641,18 +666,21 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D4">
         <v>120000</v>
@@ -661,512 +689,515 @@
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="113" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="116" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="117" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="118" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="122" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="125" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="126" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="128" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="129" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="130" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="134" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="135" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="140" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="146" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="147" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="148" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="149" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="150" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="155" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="164" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="165" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="166" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="169" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="177" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="178" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="179" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="180" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="181" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="182" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="184" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="185" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="186" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="188" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="189" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="190" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="191" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="193" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="194" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="195" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="196" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="197" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="198" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="199" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="200" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="201" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="202" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="203" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="204" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="205" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="206" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="207" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="208" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="209" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="210" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="211" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="212" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="213" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="214" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="215" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="216" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="217" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="218" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="219" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="220" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="221" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="222" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="223" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="224" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="225" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="226" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="227" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="228" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="229" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="230" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="231" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="232" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="233" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="234" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="235" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="236" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="237" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="238" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="239" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="240" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="241" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="242" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="243" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="244" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="245" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="246" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="247" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="248" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="249" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="250" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="251" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="252" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="253" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="254" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="255" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="256" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="257" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="258" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="259" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="260" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="261" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="262" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="263" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="264" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="265" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="266" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="267" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="268" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="269" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="270" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="271" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="272" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="273" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="274" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="275" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="276" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="277" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="278" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="279" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="280" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="281" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="282" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="283" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="284" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="285" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="286" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="287" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="288" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="289" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="290" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="291" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="292" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="293" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="294" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="295" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="296" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="297" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="298" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="299" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="300" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="301" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="302" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="303" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="304" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="305" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="306" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="307" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="308" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="309" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="310" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="311" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="312" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="313" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="314" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="315" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="316" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="317" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="318" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="319" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="320" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="321" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="322" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="323" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="324" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="325" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="326" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="327" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="328" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="329" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="330" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="331" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="332" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="333" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="334" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="335" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="336" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="337" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="338" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="339" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="340" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="341" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="342" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="343" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="344" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="345" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="346" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="347" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="348" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="349" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="350" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="351" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="352" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="353" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="354" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="355" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="356" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="357" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="358" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="359" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="360" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="361" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="362" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="363" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="364" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="365" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="366" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="367" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="368" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="369" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="370" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="371" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="372" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="373" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="374" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="375" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="376" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="377" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="378" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="379" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="380" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="381" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="382" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="383" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="384" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="385" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="386" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="387" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="388" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="389" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="390" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="391" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="392" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="393" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="394" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="395" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="396" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="397" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="398" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="399" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="400" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="401" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="402" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="403" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="404" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="405" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="406" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="407" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="408" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="409" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="410" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="411" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="412" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="413" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="414" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="415" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="416" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="417" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="418" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="419" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="420" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="421" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="422" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="423" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="424" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="425" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="426" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="427" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="428" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="429" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="430" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="431" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="432" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="433" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="434" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="435" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="436" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="437" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="438" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="439" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="440" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="441" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="442" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="443" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="444" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="445" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="446" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="447" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="448" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="449" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="450" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="451" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="452" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="453" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="454" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="455" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="456" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="457" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="458" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="459" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="460" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="461" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="462" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="463" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="464" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="465" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="466" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="467" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="468" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="469" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="470" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="471" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="472" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="473" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="474" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="475" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="476" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="477" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="478" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="479" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="480" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="481" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="482" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="483" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="484" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="485" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="486" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="487" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="488" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="489" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="490" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="491" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="492" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="493" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="494" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="495" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="496" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="497" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="498" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="499" spans="6:6" x14ac:dyDescent="0.25"/>
-    <row r="500" spans="6:6" x14ac:dyDescent="0.25"/>
+        <v>19</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="125" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="146" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="149" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="150" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="162" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="163" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="164" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="165" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="170" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="179" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="190" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="194" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="195" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="196" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="197" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="198" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="199" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="201" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="202" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="203" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="204" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="205" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="206" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="207" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="208" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="209" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="210" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="211" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="212" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="213" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="214" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="215" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="216" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="217" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="218" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="219" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="220" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="221" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="222" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="223" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="224" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="225" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="226" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="227" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="228" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="229" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="230" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="231" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="232" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="233" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="234" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="235" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="236" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="237" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="238" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="239" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="240" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="241" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="242" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="243" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="244" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="245" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="246" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="247" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="248" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="249" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="250" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="251" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="252" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="253" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="254" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="255" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="256" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="257" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="258" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="259" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="260" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="261" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="262" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="263" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="264" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="265" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="266" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="267" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="268" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="269" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="270" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="271" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="272" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="273" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="274" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="275" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="276" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="277" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="278" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="279" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="280" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="281" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="282" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="283" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="284" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="285" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="286" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="287" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="288" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="289" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="290" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="291" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="292" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="293" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="294" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="295" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="296" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="297" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="298" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="299" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="300" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="301" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="302" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="303" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="304" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="305" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="306" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="307" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="308" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="309" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="310" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="311" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="312" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="313" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="314" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="315" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="316" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="317" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="318" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="319" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="320" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="321" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="322" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="323" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="324" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="325" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="326" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="327" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="328" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="329" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="330" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="331" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="332" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="333" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="334" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="335" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="336" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="337" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="338" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="339" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="340" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="341" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="342" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="343" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="344" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="345" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="346" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="347" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="348" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="349" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="350" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="351" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="352" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="353" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="354" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="355" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="356" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="357" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="358" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="359" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="360" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="361" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="362" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="363" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="364" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="365" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="366" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="367" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="368" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="369" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="370" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="371" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="372" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="373" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="374" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="375" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="376" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="377" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="378" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="379" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="380" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="381" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="382" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="383" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="384" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="385" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="386" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="387" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="388" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="389" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="390" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="391" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="392" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="393" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="394" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="395" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="396" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="397" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="398" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="399" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="400" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="401" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="402" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="403" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="404" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="405" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="406" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="407" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="408" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="409" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="410" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="411" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="412" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="413" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="414" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="415" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="416" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="417" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="418" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="419" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="420" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="421" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="422" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="423" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="424" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="425" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="426" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="427" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="428" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="429" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="430" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="431" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="432" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="433" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="434" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="435" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="436" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="437" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="438" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="439" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="440" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="441" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="442" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="443" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="444" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="445" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="446" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="447" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="448" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="449" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="450" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="451" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="452" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="453" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="454" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="455" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="456" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="457" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="458" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="459" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="460" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="461" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="462" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="463" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="464" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="465" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="466" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="467" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="468" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="469" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="470" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="471" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="472" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="473" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="474" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="475" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="476" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="477" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="478" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="479" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="480" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="481" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="482" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="483" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="484" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="485" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="486" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="487" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="488" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="489" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="490" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="491" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="492" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="493" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="494" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="495" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="496" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="497" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="498" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="499" spans="7:7" x14ac:dyDescent="0.25"/>
+    <row r="500" spans="7:7" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:G1"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="F10:F500">
+    <dataValidation type="list" allowBlank="1" sqref="G10:G500">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F500">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G500">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1177,7 +1208,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
@@ -1185,87 +1216,92 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>29</v>
+      <c r="A15" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>30</v>
+      <c r="A16" s="5" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1276,7 +1312,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
@@ -1284,87 +1320,92 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>43</v>
+      <c r="A15" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>44</v>
+      <c r="A16" s="5" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>45</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/public/catalog_template.xlsx
+++ b/public/catalog_template.xlsx
@@ -15,7 +15,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="52">
   <si>
-    <t>name</t>
+    <t>product</t>
   </si>
   <si>
     <t>category</t>
@@ -96,7 +96,7 @@
     <t>Columns</t>
   </si>
   <si>
-    <t>name (required) — the name customers see and search for.</t>
+    <t>product (required) — the name customers see and search for.</t>
   </si>
   <si>
     <t>category — used to group items (e.g. Bouquets, Starters). Optional but recommended.</t>
@@ -141,7 +141,7 @@
     <t>Columnas</t>
   </si>
   <si>
-    <t>name (obligatorio) — el nombre que ven y buscan los clientes.</t>
+    <t>product (obligatorio) — el nombre que ven y buscan los clientes.</t>
   </si>
   <si>
     <t>category — agrupa los ítems (ej: Ramos, Entradas). Opcional pero recomendado.</t>
